--- a/files/2026-09-02/RTL_vs_competitors_price_diff_2026-09-02.xlsx
+++ b/files/2026-09-02/RTL_vs_competitors_price_diff_2026-09-02.xlsx
@@ -97,6 +97,780 @@
     <t xml:space="preserve">Отклонение_цены</t>
   </si>
   <si>
+    <t xml:space="preserve">08886-02805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Япония), (4л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Москва</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В наличии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5310.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5879.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4749.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-561.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4928.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-382.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">есть</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5795.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">485.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5724.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">414.15999999999985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 561 руб. (10.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Froza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08886-81875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota CVTF Fluid FE, для вариаторов, (Таиланд), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4823.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5499.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4561.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-262.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1696 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4510.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-313.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6090.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1267.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5148.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.1700000000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 313 руб. (6.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 4 510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08886-81885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Таиланд), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4407.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5024.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3971.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-436.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4084.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-322.0100000000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5325.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">918.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">под заказ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4805.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.52999999999975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 436 руб. (9.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Febi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6248.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5763.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-485.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6379.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.34000000000015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6163.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 5 763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4024610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3615.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4122.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3360.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-255.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2031 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3487.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-128.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3940.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4061.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446.42999999999984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 255 руб. (7.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550061548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes-Benz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3490.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3521.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2973.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-517.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 517 руб. (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83215A1C740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло BMW Twin Power Turbo SN 0W-30 Longlife-12 FE (C2), (Германия/Испания), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2038.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2256.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1930.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-107.53999999999996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 108 руб. (5.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 1 930.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-107.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989320911ABDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1680.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1916.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1065.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-615.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1160.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-519.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 615 руб. (36.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-36.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989440411FULW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1786.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2037.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1436.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-350.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">916 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-290.5899999999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2035.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 350 руб. (19.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989671011FBDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1238.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1412.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1033.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-205.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1235 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1077.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-160.32999999999993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 205 руб. (16.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681011FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">974.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1111.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-63.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7761 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-35.700000000000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1165.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 63 руб. (6.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681013FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5081.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5793.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-520.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">792 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-571.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 571 руб. (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691011FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1256.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1432.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1044.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-212.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1422 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1070.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-185.70000000000005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 212 руб. (16.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691013FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5471.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6237.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4857.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-614.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1793 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5049.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-422.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5241.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 614 руб. (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM10038-4EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3327.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3793.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2775.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-552.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2860.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-467.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 552 руб. (16.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2801.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3194.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2337.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-464.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2845.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.289999999999964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 464 руб. (16.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3905.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4323.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3197.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-708.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3323.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-582.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 708 руб. (18.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-18.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT5QMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">790.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">901.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-62.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2717 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">751.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-38.700000000000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">890.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.20000000000005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 62 руб. (7.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 728</t>
+  </si>
+  <si>
     <t xml:space="preserve">08269P99Z3FC1</t>
   </si>
   <si>
@@ -106,12 +880,6 @@
     <t xml:space="preserve">Honda</t>
   </si>
   <si>
-    <t xml:space="preserve">Москва</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В наличии</t>
-  </si>
-  <si>
     <t xml:space="preserve">28</t>
   </si>
   <si>
@@ -130,19 +898,13 @@
     <t xml:space="preserve">63 шт</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">6300.0</t>
   </si>
   <si>
     <t xml:space="preserve">-177.0</t>
   </si>
   <si>
-    <t xml:space="preserve">под заказ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 177 руб. (2.7%)</t>
+    <t xml:space="preserve">конкурент ниже на 177 руб. (2.7%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">Autotrade 6 300</t>
@@ -157,9 +919,6 @@
     <t xml:space="preserve">Моторное масло Toyota SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
   </si>
   <si>
-    <t xml:space="preserve">Toyota</t>
-  </si>
-  <si>
     <t xml:space="preserve">1429</t>
   </si>
   <si>
@@ -184,9 +943,6 @@
     <t xml:space="preserve">163.19999999999982</t>
   </si>
   <si>
-    <t xml:space="preserve">есть</t>
-  </si>
-  <si>
     <t xml:space="preserve">3400.0</t>
   </si>
   <si>
@@ -199,7 +955,7 @@
     <t xml:space="preserve">670.8499999999999</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 18 руб. (0.7%)</t>
+    <t xml:space="preserve">конкурент ниже на 18 руб. (0.7%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 2 549</t>
@@ -208,9 +964,6 @@
     <t xml:space="preserve">-0.7</t>
   </si>
   <si>
-    <t xml:space="preserve">Froza</t>
-  </si>
-  <si>
     <t xml:space="preserve">08880-83717</t>
   </si>
   <si>
@@ -250,7 +1003,7 @@
     <t xml:space="preserve">525.71</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 27 руб. (1.0%)</t>
+    <t xml:space="preserve">конкурент ниже на 27 руб. (1.0%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 2 561</t>
@@ -259,324 +1012,6 @@
     <t xml:space="preserve">-1.0</t>
   </si>
   <si>
-    <t xml:space="preserve">08886-02805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Япония), (4л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5310.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5879.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4749.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-561.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4928.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-382.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5795.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">485.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5724.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">414.15999999999985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 561 руб. (10.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08886-81875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota CVTF Fluid FE, для вариаторов, (Таиланд), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4823.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5499.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4561.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-262.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1696 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4510.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-313.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6090.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1267.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5148.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.1700000000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 313 руб. (6.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 4 510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08886-81885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Таиланд), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4407.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5024.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3971.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-436.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4084.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-322.0100000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5325.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">918.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4805.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.52999999999975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 436 руб. (9.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Febi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6248.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5763.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-485.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6379.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.34000000000015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6163.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 5 763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4024610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsubishi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3615.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4122.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3360.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-255.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2031 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3487.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-128.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3940.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4061.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">446.42999999999984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 255 руб. (7.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550061548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercedes-Benz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3490.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3521.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2973.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-517.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 517 руб. (14.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83215A1C740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло BMW Twin Power Turbo SN 0W-30 Longlife-12 FE (C2), (Германия/Испания), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2038.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2256.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1930.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-107.53999999999996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 108 руб. (5.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 1 930.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-107.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">83215B5BFA4</t>
   </si>
   <si>
@@ -604,7 +1039,7 @@
     <t xml:space="preserve">148.96000000000004</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 29 руб. (2.0%)</t>
+    <t xml:space="preserve">конкурент ниже на 29 руб. (2.0%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 386</t>
@@ -613,42 +1048,6 @@
     <t xml:space="preserve">-2.0</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989320911ABDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1680.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1916.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1065.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-615.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1160.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-519.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 615 руб. (36.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-36.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">A000989440411FDNE</t>
   </si>
   <si>
@@ -670,7 +1069,7 @@
     <t xml:space="preserve">-77.3599999999999</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 77 руб. (4.6%)</t>
+    <t xml:space="preserve">конкурент ниже на 77 руб. (4.6%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 606.64</t>
@@ -682,246 +1081,6 @@
     <t xml:space="preserve">-4.6</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989440411FULW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1786.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2037.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1436.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-350.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">916 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-290.5899999999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2035.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 350 руб. (19.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-19.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989671011FBDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1238.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1412.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1033.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-205.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1235 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1077.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-160.32999999999993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 205 руб. (16.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681011FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">974.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1111.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">911.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-63.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7761 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">938.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-35.700000000000045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1165.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 63 руб. (6.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681013FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5081.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5793.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-520.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">792 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-571.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 571 руб. (11.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691011FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1256.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1432.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1044.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-212.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1422 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1070.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-185.70000000000005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 212 руб. (16.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691013FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5471.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6237.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4857.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-614.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1793 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5049.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-422.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5241.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 614 руб. (11.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 857</t>
-  </si>
-  <si>
     <t xml:space="preserve">KE90799932</t>
   </si>
   <si>
@@ -958,126 +1117,12 @@
     <t xml:space="preserve">539.9000000000001</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 12 руб. (0.7%)</t>
+    <t xml:space="preserve">конкурент ниже на 12 руб. (0.7%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 1 782</t>
   </si>
   <si>
-    <t xml:space="preserve">LIM10038-4EN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3327.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3793.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2775.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-552.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2860.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-467.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 552 руб. (16.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2801.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3194.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2337.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-464.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2845.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.289999999999964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 464 руб. (16.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3905.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4323.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3197.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-708.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3323.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-582.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 708 руб. (18.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-18.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">MZ321232</t>
   </si>
   <si>
@@ -1123,58 +1168,13 @@
     <t xml:space="preserve">-475.5799999999999</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 112 руб. (3.5%)</t>
+    <t xml:space="preserve">конкурент ниже на 112 руб. (3.5%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 3 095</t>
   </si>
   <si>
     <t xml:space="preserve">-3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XT5QMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">790.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">901.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">728.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-62.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2717 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">751.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-38.700000000000045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">890.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.20000000000005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 62 руб. (7.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 728</t>
   </si>
   <si>
     <t xml:space="preserve">08234P99F4PY1</t>
@@ -1664,63 +1664,63 @@
         <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="R2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
       <c r="V2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AC2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -1729,87 +1729,87 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC3" t="s">
         <v>51</v>
-      </c>
-      <c r="H3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" t="s">
-        <v>61</v>
-      </c>
-      <c r="T3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U3" t="s">
-        <v>58</v>
-      </c>
-      <c r="V3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" t="s">
-        <v>40</v>
-      </c>
-      <c r="X3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -1818,87 +1818,87 @@
         <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" t="s">
         <v>72</v>
       </c>
-      <c r="I4" t="s">
-        <v>71</v>
-      </c>
       <c r="J4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" t="s">
+        <v>81</v>
+      </c>
+      <c r="S4" t="s">
+        <v>82</v>
+      </c>
+      <c r="T4" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4" t="s">
         <v>75</v>
       </c>
-      <c r="M4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" t="s">
-        <v>78</v>
-      </c>
-      <c r="T4" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" t="s">
-        <v>58</v>
-      </c>
-      <c r="V4" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>74</v>
-      </c>
       <c r="AB4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AC4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -1907,87 +1907,87 @@
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="O5" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" t="s">
+        <v>96</v>
+      </c>
+      <c r="T5" t="s">
+        <v>97</v>
+      </c>
+      <c r="U5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" t="s">
+        <v>39</v>
+      </c>
+      <c r="W5" t="s">
+        <v>39</v>
+      </c>
+      <c r="X5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA5" t="s">
         <v>93</v>
       </c>
-      <c r="R5" t="s">
-        <v>94</v>
-      </c>
-      <c r="S5" t="s">
-        <v>95</v>
-      </c>
-      <c r="T5" t="s">
-        <v>96</v>
-      </c>
-      <c r="U5" t="s">
-        <v>58</v>
-      </c>
-      <c r="V5" t="s">
-        <v>40</v>
-      </c>
-      <c r="W5" t="s">
-        <v>40</v>
-      </c>
-      <c r="X5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>89</v>
-      </c>
       <c r="AB5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AC5" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1996,87 +1996,87 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s">
+        <v>110</v>
+      </c>
+      <c r="N6" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>113</v>
+      </c>
+      <c r="R6" t="s">
+        <v>114</v>
+      </c>
+      <c r="S6" t="s">
+        <v>115</v>
+      </c>
+      <c r="T6" t="s">
+        <v>116</v>
+      </c>
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" t="s">
+        <v>39</v>
+      </c>
+      <c r="X6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA6" t="s">
         <v>108</v>
       </c>
-      <c r="N6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O6" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>111</v>
-      </c>
-      <c r="R6" t="s">
-        <v>94</v>
-      </c>
-      <c r="S6" t="s">
-        <v>112</v>
-      </c>
-      <c r="T6" t="s">
-        <v>113</v>
-      </c>
-      <c r="U6" t="s">
-        <v>58</v>
-      </c>
-      <c r="V6" t="s">
-        <v>40</v>
-      </c>
-      <c r="W6" t="s">
-        <v>40</v>
-      </c>
-      <c r="X6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>109</v>
-      </c>
       <c r="AB6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AC6" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -2085,87 +2085,87 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L7" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="M7" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="O7" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="P7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" t="s">
+        <v>39</v>
+      </c>
+      <c r="T7" t="s">
+        <v>39</v>
+      </c>
+      <c r="U7" t="s">
+        <v>39</v>
+      </c>
+      <c r="V7" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" t="s">
+        <v>39</v>
+      </c>
+      <c r="X7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA7" t="s">
         <v>127</v>
       </c>
-      <c r="Q7" t="s">
-        <v>128</v>
-      </c>
-      <c r="R7" t="s">
-        <v>43</v>
-      </c>
-      <c r="S7" t="s">
-        <v>129</v>
-      </c>
-      <c r="T7" t="s">
+      <c r="AB7" t="s">
         <v>130</v>
       </c>
-      <c r="U7" t="s">
-        <v>58</v>
-      </c>
-      <c r="V7" t="s">
-        <v>40</v>
-      </c>
-      <c r="W7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>133</v>
-      </c>
       <c r="AC7" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -2174,87 +2174,87 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" t="s">
+        <v>136</v>
+      </c>
+      <c r="N8" t="s">
         <v>137</v>
       </c>
-      <c r="G8" t="s">
+      <c r="O8" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y8" t="s">
         <v>138</v>
       </c>
-      <c r="H8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="Z8" t="s">
         <v>139</v>
-      </c>
-      <c r="K8" t="s">
-        <v>140</v>
-      </c>
-      <c r="L8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" t="s">
-        <v>141</v>
-      </c>
-      <c r="N8" t="s">
-        <v>142</v>
-      </c>
-      <c r="O8" t="s">
-        <v>58</v>
-      </c>
-      <c r="P8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>40</v>
-      </c>
-      <c r="R8" t="s">
-        <v>40</v>
-      </c>
-      <c r="S8" t="s">
-        <v>143</v>
-      </c>
-      <c r="T8" t="s">
-        <v>144</v>
-      </c>
-      <c r="U8" t="s">
-        <v>58</v>
-      </c>
-      <c r="V8" t="s">
-        <v>40</v>
-      </c>
-      <c r="W8" t="s">
-        <v>40</v>
-      </c>
-      <c r="X8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>146</v>
       </c>
       <c r="AA8" t="s">
         <v>140</v>
       </c>
       <c r="AB8" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AC8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2263,87 +2263,87 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" t="s">
+        <v>148</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" t="s">
+        <v>149</v>
+      </c>
+      <c r="N9" t="s">
+        <v>150</v>
+      </c>
+      <c r="O9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" t="s">
+        <v>39</v>
+      </c>
+      <c r="X9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" t="s">
         <v>151</v>
       </c>
-      <c r="G9" t="s">
+      <c r="Z9" t="s">
         <v>152</v>
       </c>
-      <c r="H9" t="s">
+      <c r="AA9" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB9" t="s">
         <v>153</v>
       </c>
-      <c r="I9" t="s">
-        <v>152</v>
-      </c>
-      <c r="J9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K9" t="s">
-        <v>155</v>
-      </c>
-      <c r="L9" t="s">
-        <v>156</v>
-      </c>
-      <c r="M9" t="s">
-        <v>157</v>
-      </c>
-      <c r="N9" t="s">
-        <v>158</v>
-      </c>
-      <c r="O9" t="s">
-        <v>58</v>
-      </c>
-      <c r="P9" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>160</v>
-      </c>
-      <c r="R9" t="s">
-        <v>161</v>
-      </c>
-      <c r="S9" t="s">
-        <v>162</v>
-      </c>
-      <c r="T9" t="s">
-        <v>163</v>
-      </c>
-      <c r="U9" t="s">
-        <v>58</v>
-      </c>
-      <c r="V9" t="s">
-        <v>40</v>
-      </c>
-      <c r="W9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X9" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>166</v>
-      </c>
       <c r="AC9" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -2352,87 +2352,87 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="I10" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="J10" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="K10" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="N10" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="O10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="Q10" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="R10" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="S10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y10" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="Z10" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AA10" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AC10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2441,87 +2441,87 @@
         <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" t="s">
+        <v>175</v>
+      </c>
+      <c r="K11" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" t="s">
+        <v>177</v>
+      </c>
+      <c r="M11" t="s">
+        <v>178</v>
+      </c>
+      <c r="N11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" t="s">
+        <v>39</v>
+      </c>
+      <c r="U11" t="s">
+        <v>39</v>
+      </c>
+      <c r="V11" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z11" t="s">
         <v>181</v>
       </c>
-      <c r="H11" t="s">
+      <c r="AA11" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB11" t="s">
         <v>182</v>
       </c>
-      <c r="I11" t="s">
-        <v>181</v>
-      </c>
-      <c r="J11" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" t="s">
-        <v>183</v>
-      </c>
-      <c r="N11" t="s">
-        <v>184</v>
-      </c>
-      <c r="O11" t="s">
-        <v>58</v>
-      </c>
-      <c r="P11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>40</v>
-      </c>
-      <c r="R11" t="s">
-        <v>40</v>
-      </c>
-      <c r="S11" t="s">
-        <v>40</v>
-      </c>
-      <c r="T11" t="s">
-        <v>40</v>
-      </c>
-      <c r="U11" t="s">
-        <v>40</v>
-      </c>
-      <c r="V11" t="s">
-        <v>40</v>
-      </c>
-      <c r="W11" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>187</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>188</v>
-      </c>
       <c r="AC11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -2530,87 +2530,87 @@
         <v>33</v>
       </c>
       <c r="F12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I12" t="s">
+        <v>186</v>
+      </c>
+      <c r="J12" t="s">
+        <v>188</v>
+      </c>
+      <c r="K12" t="s">
+        <v>189</v>
+      </c>
+      <c r="L12" t="s">
+        <v>190</v>
+      </c>
+      <c r="M12" t="s">
         <v>191</v>
       </c>
-      <c r="G12" t="s">
+      <c r="N12" t="s">
         <v>192</v>
       </c>
-      <c r="H12" t="s">
+      <c r="O12" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" t="s">
         <v>193</v>
       </c>
-      <c r="I12" t="s">
-        <v>192</v>
-      </c>
-      <c r="J12" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="Q12" t="s">
         <v>194</v>
       </c>
-      <c r="N12" t="s">
+      <c r="R12" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" t="s">
+        <v>39</v>
+      </c>
+      <c r="T12" t="s">
+        <v>39</v>
+      </c>
+      <c r="U12" t="s">
+        <v>39</v>
+      </c>
+      <c r="V12" t="s">
+        <v>39</v>
+      </c>
+      <c r="W12" t="s">
+        <v>39</v>
+      </c>
+      <c r="X12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y12" t="s">
         <v>195</v>
       </c>
-      <c r="O12" t="s">
-        <v>58</v>
-      </c>
-      <c r="P12" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>40</v>
-      </c>
-      <c r="R12" t="s">
-        <v>40</v>
-      </c>
-      <c r="S12" t="s">
+      <c r="Z12" t="s">
         <v>196</v>
       </c>
-      <c r="T12" t="s">
-        <v>197</v>
-      </c>
-      <c r="U12" t="s">
-        <v>58</v>
-      </c>
-      <c r="V12" t="s">
-        <v>40</v>
-      </c>
-      <c r="W12" t="s">
-        <v>40</v>
-      </c>
-      <c r="X12" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>199</v>
-      </c>
       <c r="AA12" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AB12" t="s">
-        <v>200</v>
+        <v>68</v>
       </c>
       <c r="AC12" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -2619,87 +2619,87 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" t="s">
+        <v>201</v>
+      </c>
+      <c r="I13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" t="s">
         <v>203</v>
       </c>
-      <c r="G13" t="s">
+      <c r="M13" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" t="s">
         <v>204</v>
       </c>
-      <c r="H13" t="s">
+      <c r="O13" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S13" t="s">
+        <v>39</v>
+      </c>
+      <c r="T13" t="s">
+        <v>39</v>
+      </c>
+      <c r="U13" t="s">
+        <v>39</v>
+      </c>
+      <c r="V13" t="s">
+        <v>39</v>
+      </c>
+      <c r="W13" t="s">
+        <v>39</v>
+      </c>
+      <c r="X13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y13" t="s">
         <v>205</v>
       </c>
-      <c r="I13" t="s">
+      <c r="Z13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA13" t="s">
         <v>204</v>
       </c>
-      <c r="J13" t="s">
+      <c r="AB13" t="s">
         <v>206</v>
       </c>
-      <c r="K13" t="s">
-        <v>207</v>
-      </c>
-      <c r="L13" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" t="s">
-        <v>208</v>
-      </c>
-      <c r="N13" t="s">
-        <v>209</v>
-      </c>
-      <c r="O13" t="s">
-        <v>58</v>
-      </c>
-      <c r="P13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>40</v>
-      </c>
-      <c r="R13" t="s">
-        <v>40</v>
-      </c>
-      <c r="S13" t="s">
-        <v>40</v>
-      </c>
-      <c r="T13" t="s">
-        <v>40</v>
-      </c>
-      <c r="U13" t="s">
-        <v>40</v>
-      </c>
-      <c r="V13" t="s">
-        <v>40</v>
-      </c>
-      <c r="W13" t="s">
-        <v>40</v>
-      </c>
-      <c r="X13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>212</v>
-      </c>
       <c r="AC13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -2708,87 +2708,87 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H14" t="s">
+        <v>211</v>
+      </c>
+      <c r="I14" t="s">
+        <v>210</v>
+      </c>
+      <c r="J14" t="s">
+        <v>212</v>
+      </c>
+      <c r="K14" t="s">
+        <v>213</v>
+      </c>
+      <c r="L14" t="s">
+        <v>214</v>
+      </c>
+      <c r="M14" t="s">
         <v>215</v>
       </c>
-      <c r="G14" t="s">
+      <c r="N14" t="s">
         <v>216</v>
       </c>
-      <c r="H14" t="s">
+      <c r="O14" t="s">
+        <v>42</v>
+      </c>
+      <c r="P14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>39</v>
+      </c>
+      <c r="R14" t="s">
+        <v>39</v>
+      </c>
+      <c r="S14" t="s">
+        <v>39</v>
+      </c>
+      <c r="T14" t="s">
+        <v>39</v>
+      </c>
+      <c r="U14" t="s">
+        <v>39</v>
+      </c>
+      <c r="V14" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" t="s">
+        <v>39</v>
+      </c>
+      <c r="X14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y14" t="s">
         <v>217</v>
       </c>
-      <c r="I14" t="s">
-        <v>216</v>
-      </c>
-      <c r="J14" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" t="s">
-        <v>40</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="Z14" t="s">
         <v>218</v>
       </c>
-      <c r="N14" t="s">
+      <c r="AA14" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB14" t="s">
         <v>219</v>
       </c>
-      <c r="O14" t="s">
-        <v>58</v>
-      </c>
-      <c r="P14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>40</v>
-      </c>
-      <c r="R14" t="s">
-        <v>40</v>
-      </c>
-      <c r="S14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T14" t="s">
-        <v>40</v>
-      </c>
-      <c r="U14" t="s">
-        <v>40</v>
-      </c>
-      <c r="V14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W14" t="s">
-        <v>40</v>
-      </c>
-      <c r="X14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>222</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>223</v>
-      </c>
       <c r="AC14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B15" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -2797,87 +2797,87 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G15" t="s">
+        <v>223</v>
+      </c>
+      <c r="H15" t="s">
+        <v>224</v>
+      </c>
+      <c r="I15" t="s">
+        <v>223</v>
+      </c>
+      <c r="J15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K15" t="s">
         <v>226</v>
       </c>
-      <c r="G15" t="s">
+      <c r="L15" t="s">
         <v>227</v>
       </c>
-      <c r="H15" t="s">
+      <c r="M15" t="s">
         <v>228</v>
       </c>
-      <c r="I15" t="s">
-        <v>227</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="N15" t="s">
         <v>229</v>
       </c>
-      <c r="K15" t="s">
+      <c r="O15" t="s">
+        <v>42</v>
+      </c>
+      <c r="P15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>39</v>
+      </c>
+      <c r="R15" t="s">
+        <v>39</v>
+      </c>
+      <c r="S15" t="s">
         <v>230</v>
       </c>
-      <c r="L15" t="s">
+      <c r="T15" t="s">
         <v>231</v>
       </c>
-      <c r="M15" t="s">
+      <c r="U15" t="s">
+        <v>42</v>
+      </c>
+      <c r="V15" t="s">
+        <v>39</v>
+      </c>
+      <c r="W15" t="s">
+        <v>39</v>
+      </c>
+      <c r="X15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y15" t="s">
         <v>232</v>
       </c>
-      <c r="N15" t="s">
+      <c r="Z15" t="s">
         <v>233</v>
       </c>
-      <c r="O15" t="s">
-        <v>58</v>
-      </c>
-      <c r="P15" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>235</v>
-      </c>
-      <c r="R15" t="s">
-        <v>236</v>
-      </c>
-      <c r="S15" t="s">
-        <v>40</v>
-      </c>
-      <c r="T15" t="s">
-        <v>40</v>
-      </c>
-      <c r="U15" t="s">
-        <v>40</v>
-      </c>
-      <c r="V15" t="s">
-        <v>40</v>
-      </c>
-      <c r="W15" t="s">
-        <v>40</v>
-      </c>
-      <c r="X15" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>238</v>
-      </c>
       <c r="AA15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AB15" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="AC15" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -2886,87 +2886,87 @@
         <v>33</v>
       </c>
       <c r="F16" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" t="s">
+        <v>238</v>
+      </c>
+      <c r="H16" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" t="s">
+        <v>238</v>
+      </c>
+      <c r="J16" t="s">
+        <v>240</v>
+      </c>
+      <c r="K16" t="s">
+        <v>241</v>
+      </c>
+      <c r="L16" t="s">
         <v>242</v>
       </c>
-      <c r="G16" t="s">
+      <c r="M16" t="s">
         <v>243</v>
       </c>
-      <c r="H16" t="s">
+      <c r="N16" t="s">
         <v>244</v>
       </c>
-      <c r="I16" t="s">
-        <v>243</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="O16" t="s">
+        <v>42</v>
+      </c>
+      <c r="P16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V16" t="s">
+        <v>39</v>
+      </c>
+      <c r="W16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y16" t="s">
         <v>245</v>
       </c>
-      <c r="K16" t="s">
+      <c r="Z16" t="s">
         <v>246</v>
       </c>
-      <c r="L16" t="s">
-        <v>247</v>
-      </c>
-      <c r="M16" t="s">
-        <v>248</v>
-      </c>
-      <c r="N16" t="s">
-        <v>249</v>
-      </c>
-      <c r="O16" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>40</v>
-      </c>
-      <c r="R16" t="s">
-        <v>40</v>
-      </c>
-      <c r="S16" t="s">
-        <v>40</v>
-      </c>
-      <c r="T16" t="s">
-        <v>40</v>
-      </c>
-      <c r="U16" t="s">
-        <v>40</v>
-      </c>
-      <c r="V16" t="s">
-        <v>40</v>
-      </c>
-      <c r="W16" t="s">
-        <v>40</v>
-      </c>
-      <c r="X16" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>251</v>
-      </c>
       <c r="AA16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AB16" t="s">
-        <v>252</v>
+        <v>182</v>
       </c>
       <c r="AC16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -2975,87 +2975,87 @@
         <v>33</v>
       </c>
       <c r="F17" t="s">
+        <v>249</v>
+      </c>
+      <c r="G17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H17" t="s">
+        <v>251</v>
+      </c>
+      <c r="I17" t="s">
+        <v>250</v>
+      </c>
+      <c r="J17" t="s">
+        <v>252</v>
+      </c>
+      <c r="K17" t="s">
+        <v>253</v>
+      </c>
+      <c r="L17" t="s">
+        <v>254</v>
+      </c>
+      <c r="M17" t="s">
+        <v>39</v>
+      </c>
+      <c r="N17" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>39</v>
+      </c>
+      <c r="R17" t="s">
+        <v>39</v>
+      </c>
+      <c r="S17" t="s">
         <v>255</v>
       </c>
-      <c r="G17" t="s">
+      <c r="T17" t="s">
         <v>256</v>
       </c>
-      <c r="H17" t="s">
+      <c r="U17" t="s">
+        <v>42</v>
+      </c>
+      <c r="V17" t="s">
+        <v>39</v>
+      </c>
+      <c r="W17" t="s">
+        <v>39</v>
+      </c>
+      <c r="X17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y17" t="s">
         <v>257</v>
       </c>
-      <c r="I17" t="s">
-        <v>256</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="Z17" t="s">
         <v>258</v>
       </c>
-      <c r="K17" t="s">
-        <v>259</v>
-      </c>
-      <c r="L17" t="s">
-        <v>260</v>
-      </c>
-      <c r="M17" t="s">
-        <v>261</v>
-      </c>
-      <c r="N17" t="s">
-        <v>262</v>
-      </c>
-      <c r="O17" t="s">
-        <v>58</v>
-      </c>
-      <c r="P17" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>264</v>
-      </c>
-      <c r="R17" t="s">
-        <v>94</v>
-      </c>
-      <c r="S17" t="s">
-        <v>40</v>
-      </c>
-      <c r="T17" t="s">
-        <v>40</v>
-      </c>
-      <c r="U17" t="s">
-        <v>40</v>
-      </c>
-      <c r="V17" t="s">
-        <v>40</v>
-      </c>
-      <c r="W17" t="s">
-        <v>40</v>
-      </c>
-      <c r="X17" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>266</v>
-      </c>
       <c r="AA17" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AB17" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="AC17" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -3064,87 +3064,87 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
+        <v>261</v>
+      </c>
+      <c r="G18" t="s">
+        <v>262</v>
+      </c>
+      <c r="H18" t="s">
+        <v>263</v>
+      </c>
+      <c r="I18" t="s">
+        <v>262</v>
+      </c>
+      <c r="J18" t="s">
+        <v>264</v>
+      </c>
+      <c r="K18" t="s">
+        <v>265</v>
+      </c>
+      <c r="L18" t="s">
+        <v>266</v>
+      </c>
+      <c r="M18" t="s">
+        <v>267</v>
+      </c>
+      <c r="N18" t="s">
+        <v>268</v>
+      </c>
+      <c r="O18" t="s">
+        <v>42</v>
+      </c>
+      <c r="P18" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18" t="s">
+        <v>39</v>
+      </c>
+      <c r="T18" t="s">
+        <v>39</v>
+      </c>
+      <c r="U18" t="s">
+        <v>39</v>
+      </c>
+      <c r="V18" t="s">
+        <v>39</v>
+      </c>
+      <c r="W18" t="s">
+        <v>39</v>
+      </c>
+      <c r="X18" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y18" t="s">
         <v>269</v>
       </c>
-      <c r="G18" t="s">
+      <c r="Z18" t="s">
         <v>270</v>
       </c>
-      <c r="H18" t="s">
+      <c r="AA18" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB18" t="s">
         <v>271</v>
       </c>
-      <c r="I18" t="s">
-        <v>270</v>
-      </c>
-      <c r="J18" t="s">
-        <v>105</v>
-      </c>
-      <c r="K18" t="s">
-        <v>272</v>
-      </c>
-      <c r="L18" t="s">
-        <v>273</v>
-      </c>
-      <c r="M18" t="s">
-        <v>108</v>
-      </c>
-      <c r="N18" t="s">
-        <v>274</v>
-      </c>
-      <c r="O18" t="s">
-        <v>58</v>
-      </c>
-      <c r="P18" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>40</v>
-      </c>
-      <c r="R18" t="s">
-        <v>40</v>
-      </c>
-      <c r="S18" t="s">
-        <v>40</v>
-      </c>
-      <c r="T18" t="s">
-        <v>40</v>
-      </c>
-      <c r="U18" t="s">
-        <v>40</v>
-      </c>
-      <c r="V18" t="s">
-        <v>40</v>
-      </c>
-      <c r="W18" t="s">
-        <v>40</v>
-      </c>
-      <c r="X18" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>274</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>276</v>
-      </c>
       <c r="AC18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>274</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -3153,87 +3153,87 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G19" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" t="s">
+        <v>277</v>
+      </c>
+      <c r="I19" t="s">
+        <v>276</v>
+      </c>
+      <c r="J19" t="s">
+        <v>278</v>
+      </c>
+      <c r="K19" t="s">
         <v>279</v>
       </c>
-      <c r="G19" t="s">
+      <c r="L19" t="s">
         <v>280</v>
       </c>
-      <c r="H19" t="s">
+      <c r="M19" t="s">
         <v>281</v>
       </c>
-      <c r="I19" t="s">
-        <v>280</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="N19" t="s">
         <v>282</v>
       </c>
-      <c r="K19" t="s">
+      <c r="O19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>39</v>
+      </c>
+      <c r="R19" t="s">
+        <v>39</v>
+      </c>
+      <c r="S19" t="s">
         <v>283</v>
       </c>
-      <c r="L19" t="s">
+      <c r="T19" t="s">
         <v>284</v>
       </c>
-      <c r="M19" t="s">
+      <c r="U19" t="s">
+        <v>42</v>
+      </c>
+      <c r="V19" t="s">
+        <v>39</v>
+      </c>
+      <c r="W19" t="s">
+        <v>39</v>
+      </c>
+      <c r="X19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y19" t="s">
         <v>285</v>
       </c>
-      <c r="N19" t="s">
+      <c r="Z19" t="s">
         <v>286</v>
       </c>
-      <c r="O19" t="s">
-        <v>58</v>
-      </c>
-      <c r="P19" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>40</v>
-      </c>
-      <c r="R19" t="s">
-        <v>40</v>
-      </c>
-      <c r="S19" t="s">
-        <v>40</v>
-      </c>
-      <c r="T19" t="s">
-        <v>40</v>
-      </c>
-      <c r="U19" t="s">
-        <v>40</v>
-      </c>
-      <c r="V19" t="s">
-        <v>40</v>
-      </c>
-      <c r="W19" t="s">
-        <v>40</v>
-      </c>
-      <c r="X19" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>288</v>
-      </c>
       <c r="AA19" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AB19" t="s">
-        <v>289</v>
+        <v>100</v>
       </c>
       <c r="AC19" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>289</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -3242,87 +3242,87 @@
         <v>33</v>
       </c>
       <c r="F20" t="s">
+        <v>290</v>
+      </c>
+      <c r="G20" t="s">
+        <v>291</v>
+      </c>
+      <c r="H20" t="s">
         <v>292</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
+        <v>291</v>
+      </c>
+      <c r="J20" t="s">
         <v>293</v>
       </c>
-      <c r="H20" t="s">
+      <c r="K20" t="s">
         <v>294</v>
       </c>
-      <c r="I20" t="s">
-        <v>293</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="L20" t="s">
         <v>295</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" t="s">
+        <v>39</v>
+      </c>
+      <c r="O20" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" t="s">
         <v>296</v>
       </c>
-      <c r="L20" t="s">
+      <c r="Q20" t="s">
         <v>297</v>
       </c>
-      <c r="M20" t="s">
+      <c r="R20" t="s">
+        <v>81</v>
+      </c>
+      <c r="S20" t="s">
+        <v>39</v>
+      </c>
+      <c r="T20" t="s">
+        <v>39</v>
+      </c>
+      <c r="U20" t="s">
+        <v>39</v>
+      </c>
+      <c r="V20" t="s">
+        <v>39</v>
+      </c>
+      <c r="W20" t="s">
+        <v>39</v>
+      </c>
+      <c r="X20" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y20" t="s">
         <v>298</v>
       </c>
-      <c r="N20" t="s">
+      <c r="Z20" t="s">
         <v>299</v>
       </c>
-      <c r="O20" t="s">
-        <v>58</v>
-      </c>
-      <c r="P20" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>40</v>
-      </c>
-      <c r="R20" t="s">
-        <v>40</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="AA20" t="s">
+        <v>297</v>
+      </c>
+      <c r="AB20" t="s">
         <v>300</v>
       </c>
-      <c r="T20" t="s">
-        <v>301</v>
-      </c>
-      <c r="U20" t="s">
-        <v>58</v>
-      </c>
-      <c r="V20" t="s">
-        <v>40</v>
-      </c>
-      <c r="W20" t="s">
-        <v>40</v>
-      </c>
-      <c r="X20" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>303</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>296</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>276</v>
-      </c>
       <c r="AC20" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B21" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C21" t="s">
-        <v>306</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -3331,76 +3331,76 @@
         <v>33</v>
       </c>
       <c r="F21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G21" t="s">
+        <v>304</v>
+      </c>
+      <c r="H21" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" t="s">
+        <v>304</v>
+      </c>
+      <c r="J21" t="s">
+        <v>306</v>
+      </c>
+      <c r="K21" t="s">
         <v>307</v>
       </c>
-      <c r="G21" t="s">
+      <c r="L21" t="s">
         <v>308</v>
       </c>
-      <c r="H21" t="s">
+      <c r="M21" t="s">
         <v>309</v>
       </c>
-      <c r="I21" t="s">
-        <v>308</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="N21" t="s">
         <v>310</v>
       </c>
-      <c r="K21" t="s">
+      <c r="O21" t="s">
+        <v>42</v>
+      </c>
+      <c r="P21" t="s">
         <v>311</v>
       </c>
-      <c r="L21" t="s">
-        <v>40</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="Q21" t="s">
         <v>312</v>
       </c>
-      <c r="N21" t="s">
+      <c r="R21" t="s">
+        <v>81</v>
+      </c>
+      <c r="S21" t="s">
         <v>313</v>
       </c>
-      <c r="O21" t="s">
-        <v>58</v>
-      </c>
-      <c r="P21" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>40</v>
-      </c>
-      <c r="R21" t="s">
-        <v>40</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>314</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
+        <v>42</v>
+      </c>
+      <c r="V21" t="s">
+        <v>39</v>
+      </c>
+      <c r="W21" t="s">
+        <v>39</v>
+      </c>
+      <c r="X21" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y21" t="s">
         <v>315</v>
       </c>
-      <c r="U21" t="s">
-        <v>58</v>
-      </c>
-      <c r="V21" t="s">
-        <v>40</v>
-      </c>
-      <c r="W21" t="s">
-        <v>40</v>
-      </c>
-      <c r="X21" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y21" t="s">
+      <c r="Z21" t="s">
         <v>316</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB21" t="s">
         <v>317</v>
       </c>
-      <c r="AA21" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>65</v>
-      </c>
       <c r="AC21" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -3447,60 +3447,60 @@
         <v>328</v>
       </c>
       <c r="O22" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S22" t="s">
-        <v>40</v>
+        <v>329</v>
       </c>
       <c r="T22" t="s">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="U22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y22" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Z22" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA22" t="s">
         <v>325</v>
       </c>
       <c r="AB22" t="s">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="AC22" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B23" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -3509,87 +3509,87 @@
         <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G23" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H23" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I23" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J23" t="s">
-        <v>336</v>
+        <v>39</v>
       </c>
       <c r="K23" t="s">
-        <v>337</v>
+        <v>39</v>
       </c>
       <c r="L23" t="s">
-        <v>338</v>
+        <v>39</v>
       </c>
       <c r="M23" t="s">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="N23" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="O23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S23" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="T23" t="s">
+        <v>342</v>
+      </c>
+      <c r="U23" t="s">
+        <v>42</v>
+      </c>
+      <c r="V23" t="s">
+        <v>39</v>
+      </c>
+      <c r="W23" t="s">
+        <v>39</v>
+      </c>
+      <c r="X23" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA23" t="s">
         <v>340</v>
       </c>
-      <c r="U23" t="s">
-        <v>58</v>
-      </c>
-      <c r="V23" t="s">
-        <v>40</v>
-      </c>
-      <c r="W23" t="s">
-        <v>40</v>
-      </c>
-      <c r="X23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>342</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>337</v>
-      </c>
       <c r="AB23" t="s">
-        <v>252</v>
+        <v>345</v>
       </c>
       <c r="AC23" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C24" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -3598,25 +3598,25 @@
         <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J24" t="s">
-        <v>348</v>
+        <v>39</v>
       </c>
       <c r="K24" t="s">
-        <v>349</v>
+        <v>39</v>
       </c>
       <c r="L24" t="s">
-        <v>350</v>
+        <v>39</v>
       </c>
       <c r="M24" t="s">
         <v>351</v>
@@ -3625,34 +3625,34 @@
         <v>352</v>
       </c>
       <c r="O24" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y24" t="s">
         <v>353</v>
@@ -3661,24 +3661,24 @@
         <v>354</v>
       </c>
       <c r="AA24" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AB24" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AC24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>359</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -3687,87 +3687,87 @@
         <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G25" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H25" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I25" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J25" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L25" t="s">
-        <v>363</v>
+        <v>39</v>
       </c>
       <c r="M25" t="s">
+        <v>365</v>
+      </c>
+      <c r="N25" t="s">
+        <v>366</v>
+      </c>
+      <c r="O25" t="s">
+        <v>42</v>
+      </c>
+      <c r="P25" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>39</v>
+      </c>
+      <c r="R25" t="s">
+        <v>39</v>
+      </c>
+      <c r="S25" t="s">
+        <v>367</v>
+      </c>
+      <c r="T25" t="s">
+        <v>368</v>
+      </c>
+      <c r="U25" t="s">
+        <v>42</v>
+      </c>
+      <c r="V25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W25" t="s">
+        <v>39</v>
+      </c>
+      <c r="X25" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA25" t="s">
         <v>364</v>
       </c>
-      <c r="N25" t="s">
-        <v>365</v>
-      </c>
-      <c r="O25" t="s">
-        <v>58</v>
-      </c>
-      <c r="P25" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>367</v>
-      </c>
-      <c r="R25" t="s">
-        <v>368</v>
-      </c>
-      <c r="S25" t="s">
-        <v>369</v>
-      </c>
-      <c r="T25" t="s">
-        <v>370</v>
-      </c>
-      <c r="U25" t="s">
-        <v>58</v>
-      </c>
-      <c r="V25" t="s">
-        <v>40</v>
-      </c>
-      <c r="W25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X25" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>372</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>362</v>
-      </c>
       <c r="AB25" t="s">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="AC25" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B26" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C26" t="s">
-        <v>376</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
@@ -3776,76 +3776,76 @@
         <v>33</v>
       </c>
       <c r="F26" t="s">
+        <v>373</v>
+      </c>
+      <c r="G26" t="s">
+        <v>374</v>
+      </c>
+      <c r="H26" t="s">
+        <v>375</v>
+      </c>
+      <c r="I26" t="s">
+        <v>374</v>
+      </c>
+      <c r="J26" t="s">
+        <v>376</v>
+      </c>
+      <c r="K26" t="s">
         <v>377</v>
       </c>
-      <c r="G26" t="s">
+      <c r="L26" t="s">
         <v>378</v>
       </c>
-      <c r="H26" t="s">
+      <c r="M26" t="s">
         <v>379</v>
       </c>
-      <c r="I26" t="s">
-        <v>378</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="N26" t="s">
         <v>380</v>
       </c>
-      <c r="K26" t="s">
+      <c r="O26" t="s">
+        <v>42</v>
+      </c>
+      <c r="P26" t="s">
         <v>381</v>
       </c>
-      <c r="L26" t="s">
+      <c r="Q26" t="s">
         <v>382</v>
       </c>
-      <c r="M26" t="s">
+      <c r="R26" t="s">
         <v>383</v>
       </c>
-      <c r="N26" t="s">
+      <c r="S26" t="s">
         <v>384</v>
       </c>
-      <c r="O26" t="s">
-        <v>58</v>
-      </c>
-      <c r="P26" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>40</v>
-      </c>
-      <c r="R26" t="s">
-        <v>40</v>
-      </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>385</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
+        <v>42</v>
+      </c>
+      <c r="V26" t="s">
+        <v>39</v>
+      </c>
+      <c r="W26" t="s">
+        <v>39</v>
+      </c>
+      <c r="X26" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y26" t="s">
         <v>386</v>
       </c>
-      <c r="U26" t="s">
-        <v>58</v>
-      </c>
-      <c r="V26" t="s">
-        <v>40</v>
-      </c>
-      <c r="W26" t="s">
-        <v>40</v>
-      </c>
-      <c r="X26" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>387</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
+        <v>377</v>
+      </c>
+      <c r="AB26" t="s">
         <v>388</v>
       </c>
-      <c r="AA26" t="s">
-        <v>381</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>147</v>
-      </c>
       <c r="AC26" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
@@ -3856,7 +3856,7 @@
         <v>390</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>289</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -3892,7 +3892,7 @@
         <v>398</v>
       </c>
       <c r="O27" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P27" t="s">
         <v>399</v>
@@ -3904,22 +3904,22 @@
         <v>401</v>
       </c>
       <c r="S27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y27" t="s">
         <v>402</v>
@@ -3934,7 +3934,7 @@
         <v>404</v>
       </c>
       <c r="AC27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -3945,7 +3945,7 @@
         <v>406</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -3957,13 +3957,13 @@
         <v>407</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>322</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>323</v>
       </c>
       <c r="I28" t="s">
-        <v>71</v>
+        <v>322</v>
       </c>
       <c r="J28" t="s">
         <v>408</v>
@@ -3972,25 +3972,25 @@
         <v>409</v>
       </c>
       <c r="L28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S28" t="s">
         <v>410</v>
@@ -3999,16 +3999,16 @@
         <v>411</v>
       </c>
       <c r="U28" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y28" t="s">
         <v>412</v>
@@ -4023,7 +4023,7 @@
         <v>414</v>
       </c>
       <c r="AC28" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
@@ -4034,7 +4034,7 @@
         <v>416</v>
       </c>
       <c r="C29" t="s">
-        <v>320</v>
+        <v>236</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -4070,34 +4070,34 @@
         <v>424</v>
       </c>
       <c r="O29" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y29" t="s">
         <v>425</v>
@@ -4112,7 +4112,7 @@
         <v>427</v>
       </c>
       <c r="AC29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
@@ -4123,7 +4123,7 @@
         <v>429</v>
       </c>
       <c r="C30" t="s">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -4144,13 +4144,13 @@
         <v>431</v>
       </c>
       <c r="J30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M30" t="s">
         <v>433</v>
@@ -4159,16 +4159,16 @@
         <v>434</v>
       </c>
       <c r="O30" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S30" t="s">
         <v>435</v>
@@ -4177,16 +4177,16 @@
         <v>436</v>
       </c>
       <c r="U30" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y30" t="s">
         <v>437</v>
@@ -4201,7 +4201,7 @@
         <v>439</v>
       </c>
       <c r="AC30" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
@@ -4212,7 +4212,7 @@
         <v>441</v>
       </c>
       <c r="C31" t="s">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="D31" t="s">
         <v>32</v>
@@ -4248,16 +4248,16 @@
         <v>449</v>
       </c>
       <c r="O31" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S31" t="s">
         <v>450</v>
@@ -4266,16 +4266,16 @@
         <v>451</v>
       </c>
       <c r="U31" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y31" t="s">
         <v>452</v>
@@ -4290,7 +4290,7 @@
         <v>454</v>
       </c>
       <c r="AC31" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
@@ -4322,31 +4322,31 @@
         <v>459</v>
       </c>
       <c r="J32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S32" t="s">
         <v>461</v>
@@ -4355,31 +4355,31 @@
         <v>462</v>
       </c>
       <c r="U32" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y32" t="s">
         <v>463</v>
       </c>
       <c r="Z32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC32" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
@@ -4411,31 +4411,31 @@
         <v>467</v>
       </c>
       <c r="J33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S33" t="s">
         <v>469</v>
@@ -4444,31 +4444,31 @@
         <v>470</v>
       </c>
       <c r="U33" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y33" t="s">
         <v>463</v>
       </c>
       <c r="Z33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC33" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
@@ -4479,7 +4479,7 @@
         <v>472</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -4491,73 +4491,73 @@
         <v>473</v>
       </c>
       <c r="G34" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>474</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="J34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y34" t="s">
         <v>463</v>
       </c>
       <c r="Z34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
@@ -4568,7 +4568,7 @@
         <v>476</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
@@ -4589,64 +4589,64 @@
         <v>477</v>
       </c>
       <c r="J35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y35" t="s">
         <v>463</v>
       </c>
       <c r="Z35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
@@ -4657,7 +4657,7 @@
         <v>480</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
         <v>32</v>
@@ -4678,64 +4678,64 @@
         <v>482</v>
       </c>
       <c r="J36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y36" t="s">
         <v>463</v>
       </c>
       <c r="Z36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37">
@@ -4767,31 +4767,31 @@
         <v>488</v>
       </c>
       <c r="J37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S37" t="s">
         <v>490</v>
@@ -4800,31 +4800,31 @@
         <v>491</v>
       </c>
       <c r="U37" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y37" t="s">
         <v>463</v>
       </c>
       <c r="Z37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC37" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
@@ -4856,31 +4856,31 @@
         <v>494</v>
       </c>
       <c r="J38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S38" t="s">
         <v>496</v>
@@ -4889,31 +4889,31 @@
         <v>497</v>
       </c>
       <c r="U38" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="V38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y38" t="s">
         <v>463</v>
       </c>
       <c r="Z38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC38" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
